--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484307_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484307_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.837</v>
+        <v>7.1566</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0307</v>
+        <v>3.9495</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8063</v>
+        <v>3.2071</v>
       </c>
       <c r="G2" t="n">
         <v>1.7443</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8387</v>
+        <v>2.1584</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9659</v>
+        <v>0.8847</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8729</v>
+        <v>1.2737</v>
       </c>
       <c r="V2" t="n">
         <v>1.4959</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.377</v>
+        <v>5.4865</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9957</v>
+        <v>3.9146</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3813</v>
+        <v>1.572</v>
       </c>
       <c r="G3" t="n">
         <v>2.624</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1122</v>
+        <v>1.2216</v>
       </c>
       <c r="T3" t="n">
-        <v>0.831</v>
+        <v>0.7499</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2811</v>
+        <v>0.4718</v>
       </c>
       <c r="V3" t="n">
         <v>0.6642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1898</v>
+        <v>5.2969</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0028</v>
+        <v>4.1645</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1869</v>
+        <v>1.1324</v>
       </c>
       <c r="G4" t="n">
         <v>4.9935</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1963</v>
+        <v>1.3034</v>
       </c>
       <c r="T4" t="n">
-        <v>0.399</v>
+        <v>0.5607</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7972</v>
+        <v>0.7428</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6093</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5545</v>
+        <v>4.1284</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0451</v>
+        <v>2.51</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5094</v>
+        <v>1.6184</v>
       </c>
       <c r="G5" t="n">
         <v>2.3238</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2074</v>
+        <v>0.7814</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2283</v>
+        <v>0.2367</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4358</v>
+        <v>0.5447</v>
       </c>
       <c r="V5" t="n">
         <v>1.2186</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4988</v>
+        <v>2.9411</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9119</v>
+        <v>1.1635</v>
       </c>
       <c r="F6" t="n">
-        <v>1.587</v>
+        <v>1.7776</v>
       </c>
       <c r="G6" t="n">
         <v>1.7124</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>2.419</v>
+        <v>1.8613</v>
       </c>
       <c r="T6" t="n">
-        <v>1.761</v>
+        <v>1.0126</v>
       </c>
       <c r="U6" t="n">
-        <v>0.658</v>
+        <v>0.8487</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5291</v>
+        <v>1.9494</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1566</v>
+        <v>1.2577</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3726</v>
+        <v>0.6917</v>
       </c>
       <c r="G7" t="n">
         <v>3.5051</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4966</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4704</v>
+        <v>-0.3693</v>
       </c>
       <c r="U7" t="n">
-        <v>1.967</v>
+        <v>1.2861</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4959</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0069</v>
+        <v>1.7364</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5077</v>
+        <v>1.0738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4992</v>
+        <v>0.6626</v>
       </c>
       <c r="G8" t="n">
         <v>0.8704</v>
@@ -1078,13 +1078,13 @@
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0589</v>
+        <v>0.6707</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6987</v>
+        <v>-0.1326</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6399</v>
+        <v>0.8033</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3422</v>
+        <v>0.9045</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2967</v>
+        <v>1.5595</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9545</v>
+        <v>-0.6549</v>
       </c>
       <c r="G9" t="n">
         <v>0.2222</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.466</v>
+        <v>0.0963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>-0.403</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1997</v>
+        <v>0.4993</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3477</v>
+        <v>-0.2933</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6536999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.306</v>
+        <v>0.3604</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1887</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.159</v>
+        <v>-0.1046</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.689</v>
+        <v>-1.1599</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.12</v>
+        <v>-1.9178</v>
       </c>
       <c r="F11" t="n">
-        <v>0.431</v>
+        <v>0.7579</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1806</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5084</v>
+        <v>0.0207</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.652</v>
+        <v>-0.4497</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1436</v>
+        <v>0.4704</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2174</v>
+        <v>-3.4603</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3838</v>
+        <v>-2.6266</v>
       </c>
       <c r="F12" t="n">
         <v>-0.8337</v>
@@ -1390,10 +1390,10 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4788</v>
+        <v>0.2359</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0522</v>
+        <v>-0.295</v>
       </c>
       <c r="U12" t="n">
         <v>0.5309</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.0812</v>
+        <v>24.6863</v>
       </c>
       <c r="E13" t="n">
-        <v>13.7897</v>
+        <v>14.395</v>
       </c>
       <c r="F13" t="n">
         <v>10.2915</v>
@@ -1468,13 +1468,13 @@
         <v>15.6274</v>
       </c>
       <c r="S13" t="n">
-        <v>8.556699999999999</v>
+        <v>9.161899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1291</v>
+        <v>1.7345</v>
       </c>
       <c r="U13" t="n">
-        <v>7.4276</v>
+        <v>7.427700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2223000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.128</v>
+        <v>1.6014</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1793</v>
+        <v>2.2804</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0513</v>
+        <v>-0.679</v>
       </c>
       <c r="G14" t="n">
         <v>1.534</v>
@@ -1546,13 +1546,13 @@
         <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3168</v>
+        <v>-0.2098</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0756</v>
+        <v>-0.9745</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3924</v>
+        <v>0.7647</v>
       </c>
       <c r="V14" t="n">
         <v>0.2772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9655</v>
+        <v>1.58</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3261</v>
+        <v>2.4272</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3606</v>
+        <v>-0.8472</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7844</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1367</v>
+        <v>-1.5221</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5598</v>
+        <v>-1.4587</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5768</v>
+        <v>-0.0634</v>
       </c>
       <c r="V15" t="n">
         <v>2.7145</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2002</v>
+        <v>0.2275</v>
       </c>
       <c r="E16" t="n">
         <v>0.5264</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3262</v>
+        <v>-0.2989</v>
       </c>
       <c r="G16" t="n">
         <v>0.2426</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2377</v>
+        <v>-0.2105</v>
       </c>
       <c r="T16" t="n">
         <v>-0.121</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1167</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8159</v>
+        <v>-1.2739</v>
       </c>
       <c r="E17" t="n">
         <v>0.1039</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9198</v>
+        <v>-1.3778</v>
       </c>
       <c r="G17" t="n">
         <v>0.3128</v>
@@ -1780,13 +1780,13 @@
         <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0235</v>
+        <v>-0.4815</v>
       </c>
       <c r="T17" t="n">
         <v>-0.7262999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2972</v>
+        <v>0.2448</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4959</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3448</v>
+        <v>-2.5055</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3878</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.7327</v>
+        <v>-3.4889</v>
       </c>
       <c r="G18" t="n">
         <v>0.0805</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6207</v>
+        <v>-0.7814</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.341</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2797</v>
+        <v>-0.0359</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2186</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6951</v>
+        <v>-2.6087</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.832</v>
+        <v>-1.8647</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8631</v>
+        <v>-0.744</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7668</v>
+        <v>-2.8296</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1328</v>
+        <v>0.5682</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.634</v>
+        <v>-3.3977</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6132</v>
+        <v>-0.1164</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6536</v>
+        <v>0.7176</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.834</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1536</v>
+        <v>-2.7131</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4792</v>
+        <v>-0.1494</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6745</v>
+        <v>-2.5638</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1469</v>
+        <v>-0.7559</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2421</v>
+        <v>-1.0488</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.2929</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0326</v>
+        <v>-2.8041</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9658</v>
+        <v>-1.832</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0668</v>
+        <v>-0.9721</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8296</v>
+        <v>-1.7668</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5682</v>
+        <v>-1.1328</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3977</v>
+        <v>-0.634</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1164</v>
+        <v>-0.6132</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7176</v>
+        <v>-0.6536</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.834</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7131</v>
+        <v>-1.1536</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1494</v>
+        <v>-0.4792</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5638</v>
+        <v>-0.6745</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1798</v>
+        <v>-0.2559</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1499</v>
+        <v>-0.2421</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.4596</v>
+        <v>-7.0071</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.053</v>
+        <v>-3.9519</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4065</v>
+        <v>-3.0552</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4547</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3872</v>
+        <v>-0.9348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9546</v>
+        <v>-0.8535</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4326</v>
+        <v>-0.0813</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0549</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.027</v>
+        <v>-9.2685</v>
       </c>
       <c r="E22" t="n">
         <v>-8.9642</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0628</v>
+        <v>-0.3043</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1511</v>
@@ -2170,13 +2170,13 @@
         <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.141</v>
+        <v>-1.3825</v>
       </c>
       <c r="T22" t="n">
         <v>-1.2572</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8838</v>
+        <v>-0.1253</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-24.0813</v>
+        <v>-22.0589</v>
       </c>
       <c r="E23" t="n">
         <v>-10.2915</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.7898</v>
+        <v>-11.7674</v>
       </c>
       <c r="G23" t="n">
         <v>-12.8167</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3705</v>
+        <v>-3.370500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-9.446200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>12.6972</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.556699999999999</v>
+        <v>-6.5344</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.427499999999999</v>
+        <v>-7.4276</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.129</v>
+        <v>0.8933</v>
       </c>
       <c r="V23" t="n">
         <v>0.2223000000000004</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484307_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484307_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7364</v>
+        <v>1.821</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0738</v>
+        <v>1.821</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6626</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8704</v>
+        <v>1.821</v>
       </c>
       <c r="H8" t="n">
-        <v>0.437</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4335</v>
+        <v>1.821</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3785</v>
+        <v>1.821</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2701</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1084</v>
+        <v>1.821</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5081</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6707</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1326</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8033</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,6 +1129,11 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2933</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.7471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3604</v>
+        <v>0.6626</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1887</v>
+        <v>-0.9505</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2696</v>
+        <v>0.437</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4583</v>
+        <v>-1.3875</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.5576</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.2701</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7126</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4045</v>
+        <v>-1.5081</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2696</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1348</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1046</v>
+        <v>0.6707</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0605</v>
+        <v>-0.1326</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.044</v>
+        <v>0.8033</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1599</v>
+        <v>-0.2933</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9178</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7579</v>
+        <v>0.3604</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1806</v>
+        <v>-0.1887</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3576</v>
+        <v>0.2696</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8229</v>
+        <v>-0.4583</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4913</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5527</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6893</v>
+        <v>0.4045</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.419</v>
+        <v>0.2696</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2702</v>
+        <v>0.1348</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0207</v>
+        <v>-0.1046</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4497</v>
+        <v>-0.0605</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4704</v>
+        <v>-0.044</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1328,12 +1378,17 @@
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4603</v>
+        <v>-1.1599</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6266</v>
+        <v>-1.9178</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8337</v>
+        <v>0.7579</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8097</v>
+        <v>-1.1806</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.329</v>
+        <v>-0.3576</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4806</v>
+        <v>-0.8229</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6321</v>
+        <v>-0.4913</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3658</v>
+        <v>0.0614</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2663</v>
+        <v>-0.5527</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1775</v>
+        <v>-0.6893</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.419</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2144</v>
+        <v>-0.2702</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2359</v>
+        <v>0.0207</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.295</v>
+        <v>-0.4497</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5309</v>
+        <v>0.4704</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.6863</v>
+        <v>-3.4603</v>
       </c>
       <c r="E13" t="n">
-        <v>14.395</v>
+        <v>-2.6266</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2915</v>
+        <v>-0.8337</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8167</v>
+        <v>-3.8097</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3706</v>
+        <v>-1.329</v>
       </c>
       <c r="I13" t="n">
-        <v>9.446400000000001</v>
+        <v>-2.4806</v>
       </c>
       <c r="J13" t="n">
-        <v>21.7569</v>
+        <v>-1.6321</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2368</v>
+        <v>-0.3658</v>
       </c>
       <c r="L13" t="n">
-        <v>15.5201</v>
+        <v>-1.2663</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.940100000000001</v>
+        <v>-2.1775</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.8663</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.0739</v>
+        <v>-1.2144</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9301</v>
+        <v>0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6973</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>15.6274</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>9.161899999999999</v>
+        <v>0.2359</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7345</v>
+        <v>-0.295</v>
       </c>
       <c r="U13" t="n">
-        <v>7.427700000000001</v>
+        <v>0.5309</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2223000000000001</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>3.601</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8234</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6014</v>
+        <v>24.6864</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2804</v>
+        <v>14.3951</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.679</v>
+        <v>10.2915</v>
       </c>
       <c r="G14" t="n">
-        <v>1.534</v>
+        <v>12.8168</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9803</v>
+        <v>3.3706</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4463</v>
+        <v>9.446400000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9312</v>
+        <v>21.757</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9483</v>
+        <v>6.2368</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9828</v>
+        <v>15.5201</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3971</v>
+        <v>-8.940100000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.968</v>
+        <v>-2.8663</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.4291</v>
+        <v>-6.0739</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-12.6973</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>15.6274</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2098</v>
+        <v>9.161899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9745</v>
+        <v>1.7345</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7647</v>
+        <v>7.427700000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-0.2223000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>3.601</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.8234</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.58</v>
+        <v>1.6014</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4272</v>
+        <v>2.2804</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8472</v>
+        <v>-0.679</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7844</v>
+        <v>1.534</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9583</v>
+        <v>1.9803</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1739</v>
+        <v>-0.4463</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1482</v>
+        <v>4.9312</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0844</v>
+        <v>2.9483</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0638</v>
+        <v>1.9828</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9326</v>
+        <v>-3.3971</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0427</v>
+        <v>-0.968</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8898</v>
+        <v>-2.4291</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5221</v>
+        <v>-0.2098</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4587</v>
+        <v>-0.9745</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0634</v>
+        <v>0.7647</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2275</v>
+        <v>1.58</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5264</v>
+        <v>2.4272</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2989</v>
+        <v>-0.8472</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2426</v>
+        <v>-0.7844</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.9583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2426</v>
+        <v>0.1739</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6475</v>
+        <v>2.1482</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0844</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6475</v>
+        <v>2.0638</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4049</v>
+        <v>-2.9326</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.0427</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4049</v>
+        <v>-1.8898</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2105</v>
+        <v>-1.5221</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.121</v>
+        <v>-1.4587</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0634</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2739</v>
+        <v>0.2275</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1039</v>
+        <v>0.5264</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3778</v>
+        <v>-0.2989</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3128</v>
+        <v>0.2426</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0954</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7827</v>
+        <v>0.2426</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8069</v>
+        <v>0.6475</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1051</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7017</v>
+        <v>0.6475</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4941</v>
+        <v>-0.4049</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4844</v>
+        <v>-0.4049</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4815</v>
+        <v>-0.2105</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2448</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5055</v>
+        <v>-1.2739</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.1039</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4889</v>
+        <v>-1.3778</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0805</v>
+        <v>0.3128</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0256</v>
+        <v>1.0954</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.7827</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6823</v>
+        <v>1.8069</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3331</v>
+        <v>1.1051</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3492</v>
+        <v>0.7017</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.6018</v>
+        <v>-1.4941</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3075</v>
+        <v>-0.0097</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2943</v>
+        <v>-1.4844</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7814</v>
+        <v>-0.4815</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0359</v>
+        <v>0.2448</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6087</v>
+        <v>-2.5055</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8647</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.744</v>
+        <v>-3.4889</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8296</v>
+        <v>0.0805</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5682</v>
+        <v>1.0256</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3977</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1164</v>
+        <v>3.6823</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7176</v>
+        <v>2.3331</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.834</v>
+        <v>1.3492</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7131</v>
+        <v>-3.6018</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1494</v>
+        <v>-1.3075</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5638</v>
+        <v>-2.2943</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7559</v>
+        <v>-0.7814</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0488</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2929</v>
+        <v>-0.0359</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8041</v>
+        <v>-2.6087</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.832</v>
+        <v>-1.8647</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9721</v>
+        <v>-0.744</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7668</v>
+        <v>-2.8296</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1328</v>
+        <v>0.5682</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.634</v>
+        <v>-3.3977</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6132</v>
+        <v>-0.1164</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6536</v>
+        <v>0.7176</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-0.834</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1536</v>
+        <v>-2.7131</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4792</v>
+        <v>-0.1494</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6745</v>
+        <v>-2.5638</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2559</v>
+        <v>-0.7559</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>-1.0488</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0138</v>
+        <v>0.2929</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0071</v>
+        <v>-2.8041</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9519</v>
+        <v>-1.832</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0552</v>
+        <v>-0.9721</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.4547</v>
+        <v>-1.7668</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7429</v>
+        <v>-1.1328</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7118</v>
+        <v>-0.634</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7228</v>
+        <v>-0.6132</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.71</v>
+        <v>-0.6536</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.732</v>
+        <v>-1.1536</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.033</v>
+        <v>-0.4792</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.699</v>
+        <v>-0.6745</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9348</v>
+        <v>-0.2559</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8535</v>
+        <v>-0.2421</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0813</v>
+        <v>-0.0138</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.2685</v>
+        <v>-7.0071</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.9642</v>
+        <v>-3.9519</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3043</v>
+        <v>-3.0552</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.1511</v>
+        <v>-4.4547</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.206</v>
+        <v>-1.7429</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.7118</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.8234</v>
+        <v>-0.7228</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.9586</v>
+        <v>-0.71</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1352</v>
+        <v>-0.0128</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3277</v>
+        <v>-3.732</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2474</v>
+        <v>-1.033</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0803</v>
+        <v>-2.699</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7348</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3825</v>
+        <v>-0.9348</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2572</v>
+        <v>-0.8535</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1253</v>
+        <v>-0.0813</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-9.2685</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-8.9642</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3043</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-5.1511</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-4.206</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.9451000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.8234</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2.9586</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.3277</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.2474</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.0803</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-2.7348</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.3825</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.2572</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.1253</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484307_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-22.0589</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-10.2915</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-11.7674</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-12.8167</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>-3.370500000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-9.446200000000001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>8.940300000000001</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>2.8663</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>6.073899999999999</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-21.7569</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-6.236899999999999</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-15.5201</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>-6.5344</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>-7.4276</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>0.8933</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>0.2223000000000004</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>3.8234</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-3.601</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
